--- a/input/mapping/111. OCB_GOLD_TCKH_SECTOR_LIST_HOP.xlsx
+++ b/input/mapping/111. OCB_GOLD_TCKH_SECTOR_LIST_HOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43CCDD8E-A876-485A-96BA-DC11C244AAA5}"/>
+  <xr:revisionPtr revIDLastSave="481" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A2B5F9E-B2E7-451A-8386-897436069E62}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
             THEN TRIM(SPLIT_PART(Ref_description, '::', 2))
         ELSE TRIM(Ref_description)
     END                                                     AS SECTOR_NAME
-FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector');</t>
+FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector')</t>
   </si>
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
@@ -878,18 +878,84 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -898,72 +964,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1309,195 +1309,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="38"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
     </row>
     <row r="2" spans="1:24" ht="21.95" customHeight="1">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="G2" s="57" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="G2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59"/>
-      <c r="L2" s="50" t="s">
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="55"/>
+      <c r="L2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="S2" s="50" t="s">
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="S2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
     </row>
     <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="G3" s="60" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="G3" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="62"/>
-      <c r="L3" s="52" t="s">
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
+      <c r="L3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="S3" s="48" t="s">
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="S3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="54"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="49"/>
-      <c r="X4" s="49"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="45"/>
+      <c r="U4" s="45"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="45"/>
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="63"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="61"/>
       <c r="K5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
       <c r="R5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="48"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="45"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="45"/>
+      <c r="W5" s="45"/>
+      <c r="X5" s="45"/>
     </row>
     <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="54"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="53"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="61"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="45"/>
+      <c r="U6" s="45"/>
+      <c r="V6" s="45"/>
+      <c r="W6" s="45"/>
+      <c r="X6" s="45"/>
     </row>
     <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
     </row>
     <row r="8" spans="1:24" ht="18" customHeight="1"/>
     <row r="9" spans="1:24" ht="18" customHeight="1">
@@ -1511,63 +1511,63 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:24" ht="18" customHeight="1">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="44"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="66"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:24" ht="18" customHeight="1">
       <c r="A12" s="6"/>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43"/>
     </row>
     <row r="13" spans="1:24" ht="18" customHeight="1">
       <c r="A13" s="7"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="43"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:24" ht="18" customHeight="1">
       <c r="A14" s="8"/>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="43"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:24" ht="18" customHeight="1">
       <c r="A15" s="9"/>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="47"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="43"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:24" ht="18" customHeight="1">
       <c r="A16" s="10"/>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="47"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="43"/>
       <c r="X16" t="s">
         <v>15</v>
       </c>
@@ -1630,91 +1630,74 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="66"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="27.95" customHeight="1">
       <c r="B29" s="39"/>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
     </row>
     <row r="30" spans="1:10" ht="27.95" customHeight="1">
       <c r="B30" s="39"/>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
       <c r="B31" s="39"/>
       <c r="C31" s="39"/>
       <c r="D31" s="39"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
     </row>
     <row r="32" spans="1:10" ht="27.95" customHeight="1">
       <c r="B32" s="39"/>
       <c r="C32" s="39"/>
       <c r="D32" s="39"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
     </row>
     <row r="33" spans="2:10" ht="27.95" customHeight="1">
       <c r="B33" s="39"/>
       <c r="C33" s="39"/>
       <c r="D33" s="39"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
     </row>
     <row r="34" spans="2:10" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="S3:X7"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="L3:Q7"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A3:E7"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="G3:J7"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="G29:J29"/>
@@ -1731,6 +1714,23 @@
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="S3:X7"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="L3:Q7"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="A3:E7"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="G3:J7"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2293,13 +2293,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2475,16 +2474,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C9CD0F-F06A-4CB4-AECA-A7F437F3D1E1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2492,5 +2492,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C9CD0F-F06A-4CB4-AECA-A7F437F3D1E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
 </file>